--- a/SGC-CKN/Excel/1d54747f-7b9f-4ff6-9078-0d0b00b0db39_Lô_CT-02_PH-159_D800_27-03-2026.xlsx
+++ b/SGC-CKN/Excel/1d54747f-7b9f-4ff6-9078-0d0b00b0db39_Lô_CT-02_PH-159_D800_27-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>PH-159</t>
+    <t>P1-159</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/1d54747f-7b9f-4ff6-9078-0d0b00b0db39_Lô_CT-02_PH-159_D800_27-03-2026.xlsx
+++ b/SGC-CKN/Excel/1d54747f-7b9f-4ff6-9078-0d0b00b0db39_Lô_CT-02_PH-159_D800_27-03-2026.xlsx
@@ -112,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">01:40
@@ -122,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">02:00
@@ -142,7 +142,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">06:15
@@ -152,7 +152,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">07:55
@@ -162,7 +162,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10:10
@@ -175,7 +175,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">11:45
